--- a/results/Int All Data -0.1/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_4_permute.xlsx
@@ -440,217 +440,217 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8136826484073446</v>
+        <v>0.8164744781180588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8155635261502914</v>
+        <v>0.8143521461390284</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8118017706643978</v>
+        <v>0.8151951815498993</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8091498828983209</v>
+        <v>0.815436635785983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8097768421459699</v>
+        <v>0.8145215749873713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7968267741085651</v>
+        <v>0.8138946157397224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7998428976441898</v>
+        <v>0.813581136115898</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7998428976441898</v>
+        <v>0.8147630292234551</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7943696932636927</v>
+        <v>0.8175843458378752</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7965386725576022</v>
+        <v>0.8132930345649352</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8016730192414132</v>
+        <v>0.8098701367757279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7976231622045569</v>
+        <v>0.810255641787293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8032404173605354</v>
+        <v>0.8086882436681708</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8017237753871365</v>
+        <v>0.8093405809886813</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7966573452602219</v>
+        <v>0.8111240552710257</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7966573452602219</v>
+        <v>0.8082053351960032</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7982247433793441</v>
+        <v>0.8169573865902263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7977418349071768</v>
+        <v>0.8175123204501346</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7968734214234441</v>
+        <v>0.8181392796977834</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7906758543346957</v>
+        <v>0.8166692850392635</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.788794976591749</v>
+        <v>0.8037192170018587</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7891804816033141</v>
+        <v>0.8046342778004704</v>
       </c>
     </row>
     <row r="24">
@@ -660,517 +660,517 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7895659866148792</v>
+        <v>0.8040073185528214</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7890110527549711</v>
+        <v>0.8018129611860503</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7886975731311466</v>
+        <v>0.8043207981766458</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7883587154344606</v>
+        <v>0.7995719565044</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7925059759319191</v>
+        <v>0.7998854361282245</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7925059759319191</v>
+        <v>0.7979325329975371</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7954713433218206</v>
+        <v>0.7874182765629871</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7999320834431036</v>
+        <v>0.7993305022683164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8323178881576244</v>
+        <v>0.7990170226444919</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.825734816057311</v>
+        <v>0.7976910787614533</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8273022141764332</v>
+        <v>0.8005631515215967</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8388289348701972</v>
+        <v>0.7955474775404054</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8334744031923198</v>
+        <v>0.7920271762905959</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8172201100683274</v>
+        <v>0.7932810947858937</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8197025689860614</v>
+        <v>0.7932810947858937</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8333516216588559</v>
+        <v>0.7932810947858937</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8151698034770376</v>
+        <v>0.7928955897743285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.81955851821058</v>
+        <v>0.7907012324075573</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.821197941717443</v>
+        <v>0.8030750973430366</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8198973759072661</v>
+        <v>0.8030750973430366</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8202108555310905</v>
+        <v>0.7981822048953093</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8122510834020154</v>
+        <v>0.7991480218396444</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8117681749298478</v>
+        <v>0.7951235428756498</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8119376037781909</v>
+        <v>0.7926157058850543</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8109251395189767</v>
+        <v>0.7929291855088787</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8057400366894425</v>
+        <v>0.7927597566605356</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7982165257176557</v>
+        <v>0.7996816864575352</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7903795351220444</v>
+        <v>0.8068663397326359</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7948402752433275</v>
+        <v>0.8022149015209925</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8108277360583744</v>
+        <v>0.8104161278861515</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8113826699182827</v>
+        <v>0.8119581479324122</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7851224069047694</v>
+        <v>0.8083445520528445</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7861348711639835</v>
+        <v>0.7945006924588451</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7885706827668384</v>
+        <v>0.8119073917866888</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7895831470260524</v>
+        <v>0.8101067570931714</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7898966266498768</v>
+        <v>0.8092637216823004</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7830000749257389</v>
+        <v>0.8026086241942462</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7798652786874944</v>
+        <v>0.8097212520816062</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7814326768066167</v>
+        <v>0.8101067570931714</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7814326768066167</v>
+        <v>0.8009184445416599</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.77955179906367</v>
+        <v>0.7862102802947724</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7798652786874944</v>
+        <v>0.7869641299067296</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7898246012621362</v>
+        <v>0.7791271393111183</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7883292285307546</v>
+        <v>0.7791271393111183</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7811191971827922</v>
+        <v>0.7705616771764114</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7453825200668047</v>
+        <v>0.7676134701976831</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7450690404429803</v>
+        <v>0.768240429445332</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7619969401295007</v>
+        <v>0.7668211909325353</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7590315727395993</v>
+        <v>0.7677575209731645</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7362916109758957</v>
+        <v>0.7665036024778666</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7356646517282468</v>
+        <v>0.7633729150704665</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7454799235274071</v>
+        <v>0.7628179812105582</v>
       </c>
     </row>
     <row r="76">
@@ -1180,717 +1180,717 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7387274225787506</v>
+        <v>0.7709897206720113</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7340252282213838</v>
+        <v>0.768990170226445</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7089468583154277</v>
+        <v>0.7664103078481086</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7217274975044895</v>
+        <v>0.7582591125408769</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6115987460815047</v>
+        <v>0.7420212547402615</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6115987460815047</v>
+        <v>0.7494940095663249</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6018808777429467</v>
+        <v>0.748434897992232</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6018808777429467</v>
+        <v>0.7501209688139738</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5780564263322884</v>
+        <v>0.7273694056455335</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5780564263322884</v>
+        <v>0.6940644313015567</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5711598746081504</v>
+        <v>0.6957292328812814</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.567398119122257</v>
+        <v>0.6875149549357935</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5695924764890282</v>
+        <v>0.6807158066722578</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5717868338557994</v>
+        <v>0.6744249449537515</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5630094043887147</v>
+        <v>0.6762337973089575</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5642633228840126</v>
+        <v>0.6762337973089575</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.6778396250812703</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5015673981191222</v>
+        <v>0.6817920786575241</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5015673981191222</v>
+        <v>0.7252978298122263</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5012539184952978</v>
+        <v>0.713457629494638</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5025078369905956</v>
+        <v>0.713457629494638</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5006269592476489</v>
+        <v>0.6972664190089016</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5</v>
+        <v>0.5233620870927121</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5</v>
+        <v>0.5355919012527101</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5</v>
+        <v>0.5442040107022958</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5</v>
+        <v>0.536434936663581</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5</v>
+        <v>0.5351810181682832</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5385277817389055</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.5304239588343489</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5015673981191222</v>
+        <v>0.5365666609465296</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5009404388714733</v>
+        <v>0.5365666609465296</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5009404388714733</v>
+        <v>0.5362236944189992</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5012539184952978</v>
+        <v>0.5280306857155287</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.501808852355206</v>
+        <v>0.5292846042108265</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.501808852355206</v>
+        <v>0.5282934091936299</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5021943573667712</v>
+        <v>0.5272809449344158</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5021943573667712</v>
+        <v>0.5206217386155174</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5002414542360838</v>
+        <v>0.5177750439282356</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4983646853239813</v>
+        <v>0.5154620138588447</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5011098677198165</v>
+        <v>0.5166185288935402</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5011098677198165</v>
+        <v>0.5137972122791201</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5011098677198165</v>
+        <v>0.5128567734076468</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5009658169443351</v>
+        <v>0.5131702530314712</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4986274088020825</v>
+        <v>0.5079131248141963</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4986274088020825</v>
+        <v>0.5086121094495859</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4982419037905173</v>
+        <v>0.5070447113304636</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.498483358026601</v>
+        <v>0.5093323633269928</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4996144949884349</v>
+        <v>0.5160848642756494</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5</v>
+        <v>0.5131915222734886</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5</v>
+        <v>0.5091883125515114</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5</v>
+        <v>0.5091883125515114</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5</v>
+        <v>0.5091883125515114</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5</v>
+        <v>0.5091883125515114</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5</v>
+        <v>0.5121536799414129</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.516614420062696</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.5125645630258397</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.5099593225746417</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5062695924764891</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.503448275862069</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.503448275862069</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.503448275862069</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.503448275862069</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.503448275862069</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.503448275862069</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5031347962382445</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5031347962382445</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5031347962382445</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5021943573667712</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5025078369905956</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.5028213166144201</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5009404388714733</v>
       </c>
     </row>
     <row r="148">
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5006269592476489</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
